--- a/data/dividends_info_20260826.xlsx
+++ b/data/dividends_info_20260826.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>42.64500045776367</v>
+        <v>42.31999969482422</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2110446688566401</v>
+        <v>0.2126654079607829</v>
       </c>
       <c r="J2" t="n">
         <v>201</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.69999694824219</v>
+        <v>65.84999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.049475310385974</v>
+        <v>1.063022044374228</v>
       </c>
       <c r="J3" t="n">
         <v>180</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.4880000054836273</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.8196721219369336</v>
       </c>
       <c r="J5" t="n">
         <v>110</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42.64500045776367</v>
+        <v>42.31999969482422</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2110446688566401</v>
+        <v>0.2126654079607829</v>
       </c>
       <c r="J6" t="n">
         <v>110</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.130000114440918</v>
+        <v>2.115000009536743</v>
       </c>
       <c r="I7" t="n">
-        <v>3.615023279949961</v>
+        <v>3.640661922118176</v>
       </c>
       <c r="J7" t="n">
         <v>89</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.90500068664551</v>
+        <v>23.02499961853027</v>
       </c>
       <c r="I8" t="n">
-        <v>1.178781890006318</v>
+        <v>1.172638455909927</v>
       </c>
       <c r="J8" t="n">
         <v>89</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.28000068664551</v>
+        <v>23.14999961853027</v>
       </c>
       <c r="I9" t="n">
-        <v>2.534364186417105</v>
+        <v>2.548596154307226</v>
       </c>
       <c r="J9" t="n">
         <v>89</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.920000076293945</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I10" t="n">
-        <v>3.378378334839559</v>
+        <v>3.412969205515265</v>
       </c>
       <c r="J10" t="n">
         <v>82</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.52000045776367</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="I11" t="n">
-        <v>4.372623383875653</v>
+        <v>4.360189494631266</v>
       </c>
       <c r="J11" t="n">
         <v>61</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4819999933242798</v>
+        <v>0.4880000054836273</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8298755301660101</v>
+        <v>0.8196721219369336</v>
       </c>
       <c r="J13" t="n">
         <v>54</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.079999923706055</v>
+        <v>5.039999961853027</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7480315072972982</v>
+        <v>0.753968259674922</v>
       </c>
       <c r="J15" t="n">
         <v>33</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>22.90999984741211</v>
+        <v>23.02499961853027</v>
       </c>
       <c r="I16" t="n">
-        <v>1.178524669569122</v>
+        <v>1.172638455909927</v>
       </c>
       <c r="J16" t="n">
         <v>26</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.078000068664551</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="I17" t="n">
-        <v>2.743022046030618</v>
+        <v>2.753623277209751</v>
       </c>
       <c r="J17" t="n">
         <v>26</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>42.64500045776367</v>
+        <v>42.31999969482422</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2110446688566401</v>
+        <v>0.2126654079607829</v>
       </c>
       <c r="J18" t="n">
         <v>26</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>91.15000152587891</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="I19" t="n">
-        <v>1.459133272337239</v>
+        <v>1.42398284611536</v>
       </c>
       <c r="J19" t="n">
         <v>26</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6.159999847412109</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I20" t="n">
-        <v>4.870129990766698</v>
+        <v>4.901960875977926</v>
       </c>
       <c r="J20" t="n">
         <v>19</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4819999933242798</v>
+        <v>0.4880000054836273</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8298755301660101</v>
+        <v>0.8196721219369336</v>
       </c>
       <c r="J21" t="n">
         <v>-2</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.079999923706055</v>
+        <v>5.039999961853027</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7480315072972982</v>
+        <v>0.753968259674922</v>
       </c>
       <c r="J23" t="n">
         <v>-23</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.960000038146973</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>4.194630845635492</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="J26" t="n">
         <v>-30</v>
@@ -3363,7 +3363,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3373,14 +3373,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3397,7 +3397,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ENTERA</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>ENTERA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3516,7 +3516,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3533,7 +3533,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3550,7 +3550,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3560,14 +3560,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3618,7 +3618,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3635,7 +3635,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3652,7 +3652,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3669,7 +3669,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3703,7 +3703,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3720,7 +3720,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3737,7 +3737,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3754,7 +3754,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3771,7 +3771,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,14 +3781,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3798,14 +3798,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3822,7 +3822,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3839,7 +3839,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3856,7 +3856,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3890,7 +3890,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3907,7 +3907,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3924,7 +3924,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3941,7 +3941,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3975,7 +3975,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4009,7 +4009,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4026,7 +4026,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4043,7 +4043,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4053,14 +4053,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4094,7 +4094,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4111,7 +4111,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4149,384 +4149,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Allcore S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BASTOGI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BESTBE HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cloudia Research S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ESAUTOMOTION S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Ecomembrane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FOPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ILPRA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MIT SIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Maps S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Pasquarelli Auto S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Predict S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SBE-Varvit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Smart Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Somec S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Svas Biosana S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>VINEXT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>gAIn360 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>